--- a/data/Protein location MitoMiner v3.1.xlsx
+++ b/data/Protein location MitoMiner v3.1.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luho/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/De-nevo-protein-3D-structure-yeast/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{8E85CF71-C471-BE42-B224-ABBE36E2AD3E}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="32" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79B2D3D-D1E2-D648-B26A-85889270E58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="1860" windowWidth="28040" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23040" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gene_localization_evidence_yeas" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">gene_localization_evidence_yeas!$M$1:$M$1235</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -12194,6 +12197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:N1235"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -12205,7 +12209,7 @@
     <col min="8" max="8" width="11.6640625" customWidth="1"/>
     <col min="9" max="9" width="14.1640625" customWidth="1"/>
     <col min="10" max="10" width="17.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="28.1640625" customWidth="1"/>
+    <col min="11" max="11" width="38.33203125" customWidth="1"/>
     <col min="12" max="12" width="29.5" customWidth="1"/>
     <col min="13" max="13" width="53" customWidth="1"/>
     <col min="14" max="14" width="39.83203125" customWidth="1"/>
@@ -12563,7 +12567,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -12607,7 +12611,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -12695,7 +12699,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -12739,7 +12743,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -12783,7 +12787,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -12959,7 +12963,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -13003,7 +13007,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -13047,7 +13051,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>90</v>
       </c>
@@ -13179,7 +13183,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>100</v>
       </c>
@@ -13223,7 +13227,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>103</v>
       </c>
@@ -13267,7 +13271,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>106</v>
       </c>
@@ -13443,7 +13447,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>120</v>
       </c>
@@ -13487,7 +13491,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>123</v>
       </c>
@@ -13531,7 +13535,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>127</v>
       </c>
@@ -13575,7 +13579,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>130</v>
       </c>
@@ -13751,7 +13755,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>145</v>
       </c>
@@ -13795,7 +13799,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>148</v>
       </c>
@@ -13883,7 +13887,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>156</v>
       </c>
@@ -13927,7 +13931,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>159</v>
       </c>
@@ -14059,7 +14063,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>169</v>
       </c>
@@ -14103,7 +14107,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>173</v>
       </c>
@@ -14191,7 +14195,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>179</v>
       </c>
@@ -14235,7 +14239,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>182</v>
       </c>
@@ -14279,7 +14283,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>185</v>
       </c>
@@ -14323,7 +14327,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>188</v>
       </c>
@@ -14367,7 +14371,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>191</v>
       </c>
@@ -14411,7 +14415,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>194</v>
       </c>
@@ -14455,7 +14459,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>197</v>
       </c>
@@ -14499,7 +14503,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>200</v>
       </c>
@@ -14543,7 +14547,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>203</v>
       </c>
@@ -14675,7 +14679,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>212</v>
       </c>
@@ -14763,7 +14767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>219</v>
       </c>
@@ -14807,7 +14811,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>222</v>
       </c>
@@ -14895,7 +14899,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>229</v>
       </c>
@@ -14939,7 +14943,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>233</v>
       </c>
@@ -15027,7 +15031,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>239</v>
       </c>
@@ -15071,7 +15075,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>242</v>
       </c>
@@ -15159,7 +15163,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>249</v>
       </c>
@@ -15291,7 +15295,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>259</v>
       </c>
@@ -15335,7 +15339,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>262</v>
       </c>
@@ -15379,7 +15383,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>265</v>
       </c>
@@ -15423,7 +15427,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>269</v>
       </c>
@@ -15511,7 +15515,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>275</v>
       </c>
@@ -15555,7 +15559,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>278</v>
       </c>
@@ -15643,7 +15647,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>285</v>
       </c>
@@ -15687,7 +15691,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>288</v>
       </c>
@@ -15731,7 +15735,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>292</v>
       </c>
@@ -15775,7 +15779,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>296</v>
       </c>
@@ -15819,7 +15823,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>299</v>
       </c>
@@ -15863,7 +15867,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>302</v>
       </c>
@@ -15907,7 +15911,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>305</v>
       </c>
@@ -15951,7 +15955,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>308</v>
       </c>
@@ -15995,7 +15999,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>311</v>
       </c>
@@ -16039,7 +16043,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>314</v>
       </c>
@@ -16083,7 +16087,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>318</v>
       </c>
@@ -16215,7 +16219,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>327</v>
       </c>
@@ -16259,7 +16263,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>330</v>
       </c>
@@ -16347,7 +16351,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>337</v>
       </c>
@@ -16391,7 +16395,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>340</v>
       </c>
@@ -16435,7 +16439,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>344</v>
       </c>
@@ -16479,7 +16483,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>347</v>
       </c>
@@ -16523,7 +16527,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>350</v>
       </c>
@@ -16567,7 +16571,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>353</v>
       </c>
@@ -16611,7 +16615,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>356</v>
       </c>
@@ -16743,7 +16747,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>367</v>
       </c>
@@ -16787,7 +16791,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>370</v>
       </c>
@@ -16831,7 +16835,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>373</v>
       </c>
@@ -16872,7 +16876,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>375</v>
       </c>
@@ -16960,7 +16964,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>381</v>
       </c>
@@ -17004,7 +17008,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>384</v>
       </c>
@@ -17048,7 +17052,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>387</v>
       </c>
@@ -17092,7 +17096,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>390</v>
       </c>
@@ -17224,7 +17228,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>399</v>
       </c>
@@ -17268,7 +17272,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>402</v>
       </c>
@@ -17356,7 +17360,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>408</v>
       </c>
@@ -17400,7 +17404,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>412</v>
       </c>
@@ -17444,7 +17448,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>415</v>
       </c>
@@ -17488,7 +17492,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>418</v>
       </c>
@@ -17532,7 +17536,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>421</v>
       </c>
@@ -17576,7 +17580,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>424</v>
       </c>
@@ -17664,7 +17668,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>430</v>
       </c>
@@ -17796,7 +17800,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>440</v>
       </c>
@@ -17840,7 +17844,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>443</v>
       </c>
@@ -17884,7 +17888,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>446</v>
       </c>
@@ -17928,7 +17932,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>449</v>
       </c>
@@ -17972,7 +17976,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>452</v>
       </c>
@@ -18016,7 +18020,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>455</v>
       </c>
@@ -18060,7 +18064,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>458</v>
       </c>
@@ -18104,7 +18108,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>461</v>
       </c>
@@ -18148,7 +18152,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>464</v>
       </c>
@@ -18236,7 +18240,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>471</v>
       </c>
@@ -18368,7 +18372,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>481</v>
       </c>
@@ -18412,7 +18416,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>485</v>
       </c>
@@ -18456,7 +18460,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>488</v>
       </c>
@@ -18544,7 +18548,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>495</v>
       </c>
@@ -18588,7 +18592,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>498</v>
       </c>
@@ -18632,7 +18636,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>501</v>
       </c>
@@ -18676,7 +18680,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>504</v>
       </c>
@@ -18720,7 +18724,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>507</v>
       </c>
@@ -18764,7 +18768,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>510</v>
       </c>
@@ -18808,7 +18812,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>513</v>
       </c>
@@ -18852,7 +18856,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>516</v>
       </c>
@@ -18896,7 +18900,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>520</v>
       </c>
@@ -18984,7 +18988,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>526</v>
       </c>
@@ -19028,7 +19032,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>529</v>
       </c>
@@ -19072,7 +19076,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>532</v>
       </c>
@@ -19160,7 +19164,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>538</v>
       </c>
@@ -19204,7 +19208,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>542</v>
       </c>
@@ -19248,7 +19252,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>545</v>
       </c>
@@ -19292,7 +19296,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>549</v>
       </c>
@@ -19336,7 +19340,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>552</v>
       </c>
@@ -19380,7 +19384,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>555</v>
       </c>
@@ -19424,7 +19428,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>558</v>
       </c>
@@ -19468,7 +19472,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>561</v>
       </c>
@@ -19688,7 +19692,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>577</v>
       </c>
@@ -19776,7 +19780,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>584</v>
       </c>
@@ -19820,7 +19824,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>587</v>
       </c>
@@ -19908,7 +19912,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>593</v>
       </c>
@@ -19952,7 +19956,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>596</v>
       </c>
@@ -19996,7 +20000,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>600</v>
       </c>
@@ -20084,7 +20088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>607</v>
       </c>
@@ -20128,7 +20132,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>610</v>
       </c>
@@ -20172,7 +20176,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>614</v>
       </c>
@@ -20260,7 +20264,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>620</v>
       </c>
@@ -20348,7 +20352,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>626</v>
       </c>
@@ -20392,7 +20396,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>629</v>
       </c>
@@ -20436,7 +20440,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>632</v>
       </c>
@@ -20568,7 +20572,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>642</v>
       </c>
@@ -20612,7 +20616,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>645</v>
       </c>
@@ -20656,7 +20660,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>648</v>
       </c>
@@ -20744,7 +20748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>654</v>
       </c>
@@ -20788,7 +20792,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>657</v>
       </c>
@@ -20876,7 +20880,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>663</v>
       </c>
@@ -20920,7 +20924,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>666</v>
       </c>
@@ -20964,7 +20968,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>669</v>
       </c>
@@ -21008,7 +21012,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>672</v>
       </c>
@@ -21052,7 +21056,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>675</v>
       </c>
@@ -21096,7 +21100,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>678</v>
       </c>
@@ -21140,7 +21144,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>681</v>
       </c>
@@ -21184,7 +21188,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>684</v>
       </c>
@@ -21228,7 +21232,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>687</v>
       </c>
@@ -21272,7 +21276,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>690</v>
       </c>
@@ -21316,7 +21320,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>693</v>
       </c>
@@ -21360,7 +21364,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>696</v>
       </c>
@@ -21404,7 +21408,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>699</v>
       </c>
@@ -21492,7 +21496,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>705</v>
       </c>
@@ -21536,7 +21540,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>708</v>
       </c>
@@ -21580,7 +21584,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>711</v>
       </c>
@@ -21668,7 +21672,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>717</v>
       </c>
@@ -21712,7 +21716,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>720</v>
       </c>
@@ -21756,7 +21760,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>723</v>
       </c>
@@ -21800,7 +21804,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>726</v>
       </c>
@@ -21844,7 +21848,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>729</v>
       </c>
@@ -21888,7 +21892,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>732</v>
       </c>
@@ -21932,7 +21936,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>735</v>
       </c>
@@ -21976,7 +21980,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>738</v>
       </c>
@@ -22020,7 +22024,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>741</v>
       </c>
@@ -22064,7 +22068,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>744</v>
       </c>
@@ -22152,7 +22156,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>750</v>
       </c>
@@ -22196,7 +22200,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>753</v>
       </c>
@@ -22240,7 +22244,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>756</v>
       </c>
@@ -22284,7 +22288,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>759</v>
       </c>
@@ -22328,7 +22332,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>762</v>
       </c>
@@ -22372,7 +22376,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>765</v>
       </c>
@@ -22416,7 +22420,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>768</v>
       </c>
@@ -22460,7 +22464,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>771</v>
       </c>
@@ -22504,7 +22508,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>774</v>
       </c>
@@ -22548,7 +22552,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>777</v>
       </c>
@@ -22592,7 +22596,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>780</v>
       </c>
@@ -22636,7 +22640,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>783</v>
       </c>
@@ -22724,7 +22728,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>789</v>
       </c>
@@ -22768,7 +22772,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>792</v>
       </c>
@@ -22812,7 +22816,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>795</v>
       </c>
@@ -22900,7 +22904,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>801</v>
       </c>
@@ -23032,7 +23036,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>811</v>
       </c>
@@ -23296,7 +23300,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>831</v>
       </c>
@@ -23340,7 +23344,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>834</v>
       </c>
@@ -23513,7 +23517,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>845</v>
       </c>
@@ -23557,7 +23561,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>848</v>
       </c>
@@ -23601,7 +23605,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>851</v>
       </c>
@@ -23645,7 +23649,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>854</v>
       </c>
@@ -23689,7 +23693,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>857</v>
       </c>
@@ -23733,7 +23737,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>860</v>
       </c>
@@ -23821,7 +23825,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>866</v>
       </c>
@@ -23865,7 +23869,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>869</v>
       </c>
@@ -23953,7 +23957,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>875</v>
       </c>
@@ -23997,7 +24001,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>878</v>
       </c>
@@ -24041,7 +24045,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>881</v>
       </c>
@@ -24129,7 +24133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>887</v>
       </c>
@@ -24170,7 +24174,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>889</v>
       </c>
@@ -24214,7 +24218,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>892</v>
       </c>
@@ -24258,7 +24262,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>895</v>
       </c>
@@ -24302,7 +24306,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>898</v>
       </c>
@@ -24390,7 +24394,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>904</v>
       </c>
@@ -24434,7 +24438,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>907</v>
       </c>
@@ -24478,7 +24482,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>910</v>
       </c>
@@ -24522,7 +24526,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>913</v>
       </c>
@@ -24566,7 +24570,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>916</v>
       </c>
@@ -24698,7 +24702,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>925</v>
       </c>
@@ -24786,7 +24790,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>931</v>
       </c>
@@ -24827,7 +24831,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>933</v>
       </c>
@@ -24871,7 +24875,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>936</v>
       </c>
@@ -24915,7 +24919,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>939</v>
       </c>
@@ -24959,7 +24963,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>942</v>
       </c>
@@ -25003,7 +25007,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>945</v>
       </c>
@@ -25047,7 +25051,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>948</v>
       </c>
@@ -25091,7 +25095,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>951</v>
       </c>
@@ -25135,7 +25139,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>954</v>
       </c>
@@ -25179,7 +25183,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>957</v>
       </c>
@@ -25223,7 +25227,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>960</v>
       </c>
@@ -25267,7 +25271,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>963</v>
       </c>
@@ -25311,7 +25315,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>966</v>
       </c>
@@ -25355,7 +25359,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>969</v>
       </c>
@@ -25399,7 +25403,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>973</v>
       </c>
@@ -25443,7 +25447,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>976</v>
       </c>
@@ -25487,7 +25491,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>979</v>
       </c>
@@ -25531,7 +25535,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>983</v>
       </c>
@@ -25575,7 +25579,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>986</v>
       </c>
@@ -25663,7 +25667,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>993</v>
       </c>
@@ -25707,7 +25711,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>996</v>
       </c>
@@ -25751,7 +25755,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>999</v>
       </c>
@@ -25795,7 +25799,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>1002</v>
       </c>
@@ -25883,7 +25887,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>1008</v>
       </c>
@@ -25971,7 +25975,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>1014</v>
       </c>
@@ -26015,7 +26019,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>1017</v>
       </c>
@@ -26059,7 +26063,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>1020</v>
       </c>
@@ -26103,7 +26107,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>1023</v>
       </c>
@@ -26147,7 +26151,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>1026</v>
       </c>
@@ -26191,7 +26195,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>1029</v>
       </c>
@@ -26279,7 +26283,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>1036</v>
       </c>
@@ -26367,7 +26371,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>1042</v>
       </c>
@@ -26411,7 +26415,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>1045</v>
       </c>
@@ -26455,7 +26459,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>1048</v>
       </c>
@@ -26543,7 +26547,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>1054</v>
       </c>
@@ -26587,7 +26591,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>1057</v>
       </c>
@@ -26675,7 +26679,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>1063</v>
       </c>
@@ -26763,7 +26767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>1069</v>
       </c>
@@ -26807,7 +26811,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>1072</v>
       </c>
@@ -26851,7 +26855,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>1075</v>
       </c>
@@ -26895,7 +26899,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>1078</v>
       </c>
@@ -26939,7 +26943,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>1081</v>
       </c>
@@ -26983,7 +26987,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>1084</v>
       </c>
@@ -27027,7 +27031,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>1087</v>
       </c>
@@ -27071,7 +27075,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>1090</v>
       </c>
@@ -27115,7 +27119,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>1094</v>
       </c>
@@ -27159,7 +27163,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>1097</v>
       </c>
@@ -27203,7 +27207,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>1100</v>
       </c>
@@ -27247,7 +27251,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>1103</v>
       </c>
@@ -27291,7 +27295,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>1106</v>
       </c>
@@ -27335,7 +27339,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>1109</v>
       </c>
@@ -27379,7 +27383,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>1112</v>
       </c>
@@ -27423,7 +27427,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>1115</v>
       </c>
@@ -27508,7 +27512,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>1120</v>
       </c>
@@ -27596,7 +27600,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>1126</v>
       </c>
@@ -27640,7 +27644,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>1129</v>
       </c>
@@ -27728,7 +27732,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>1135</v>
       </c>
@@ -27816,7 +27820,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>1141</v>
       </c>
@@ -27860,7 +27864,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>1144</v>
       </c>
@@ -27948,7 +27952,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>1150</v>
       </c>
@@ -27992,7 +27996,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>1153</v>
       </c>
@@ -28036,7 +28040,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>1156</v>
       </c>
@@ -28080,7 +28084,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>1159</v>
       </c>
@@ -28168,7 +28172,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>1164</v>
       </c>
@@ -28212,7 +28216,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>1167</v>
       </c>
@@ -28300,7 +28304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>1175</v>
       </c>
@@ -28388,7 +28392,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>1181</v>
       </c>
@@ -28520,7 +28524,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>1190</v>
       </c>
@@ -28564,7 +28568,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>1193</v>
       </c>
@@ -28608,7 +28612,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>1196</v>
       </c>
@@ -28652,7 +28656,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>1199</v>
       </c>
@@ -28740,7 +28744,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>1205</v>
       </c>
@@ -28781,7 +28785,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>1207</v>
       </c>
@@ -28913,7 +28917,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>1217</v>
       </c>
@@ -28957,7 +28961,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>1220</v>
       </c>
@@ -29089,7 +29093,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>1230</v>
       </c>
@@ -29133,7 +29137,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>1233</v>
       </c>
@@ -29177,7 +29181,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>1236</v>
       </c>
@@ -29265,7 +29269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>1242</v>
       </c>
@@ -29397,7 +29401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>1251</v>
       </c>
@@ -29441,7 +29445,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>1254</v>
       </c>
@@ -29485,7 +29489,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>1257</v>
       </c>
@@ -29526,7 +29530,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>1259</v>
       </c>
@@ -29570,7 +29574,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>1262</v>
       </c>
@@ -29614,7 +29618,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>1264</v>
       </c>
@@ -29658,7 +29662,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>1267</v>
       </c>
@@ -29702,7 +29706,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>1270</v>
       </c>
@@ -29746,7 +29750,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>1273</v>
       </c>
@@ -29790,7 +29794,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>1276</v>
       </c>
@@ -29834,7 +29838,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>1280</v>
       </c>
@@ -29878,7 +29882,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>1283</v>
       </c>
@@ -30010,7 +30014,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>1293</v>
       </c>
@@ -30054,7 +30058,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>1296</v>
       </c>
@@ -30098,7 +30102,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>1299</v>
       </c>
@@ -30186,7 +30190,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>1305</v>
       </c>
@@ -30230,7 +30234,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>1308</v>
       </c>
@@ -30274,7 +30278,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>1311</v>
       </c>
@@ -30318,7 +30322,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>1314</v>
       </c>
@@ -30362,7 +30366,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>1317</v>
       </c>
@@ -30450,7 +30454,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>1323</v>
       </c>
@@ -30494,7 +30498,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>1326</v>
       </c>
@@ -30582,7 +30586,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>1332</v>
       </c>
@@ -30626,7 +30630,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>1336</v>
       </c>
@@ -30670,7 +30674,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>1339</v>
       </c>
@@ -30714,7 +30718,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>1342</v>
       </c>
@@ -30758,7 +30762,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>1346</v>
       </c>
@@ -30802,7 +30806,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>1349</v>
       </c>
@@ -30890,7 +30894,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>1355</v>
       </c>
@@ -30934,7 +30938,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>1358</v>
       </c>
@@ -30978,7 +30982,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>1362</v>
       </c>
@@ -31022,7 +31026,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>1365</v>
       </c>
@@ -31110,7 +31114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>1371</v>
       </c>
@@ -31154,7 +31158,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>1374</v>
       </c>
@@ -31242,7 +31246,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>1380</v>
       </c>
@@ -31286,7 +31290,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>1383</v>
       </c>
@@ -31330,7 +31334,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>1386</v>
       </c>
@@ -31374,7 +31378,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>1389</v>
       </c>
@@ -31462,7 +31466,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="439" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>1395</v>
       </c>
@@ -31550,7 +31554,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="441" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>1402</v>
       </c>
@@ -31594,7 +31598,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="442" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>1405</v>
       </c>
@@ -31726,7 +31730,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="445" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>1414</v>
       </c>
@@ -31770,7 +31774,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>1417</v>
       </c>
@@ -31814,7 +31818,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>1420</v>
       </c>
@@ -31858,7 +31862,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>1423</v>
       </c>
@@ -31902,7 +31906,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="449" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>1426</v>
       </c>
@@ -31946,7 +31950,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="450" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>1430</v>
       </c>
@@ -31990,7 +31994,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="451" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>1433</v>
       </c>
@@ -32034,7 +32038,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="452" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>1436</v>
       </c>
@@ -32078,7 +32082,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="453" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>1439</v>
       </c>
@@ -32122,7 +32126,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="454" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>1442</v>
       </c>
@@ -32210,7 +32214,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="456" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>1448</v>
       </c>
@@ -32254,7 +32258,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="457" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>1451</v>
       </c>
@@ -32298,7 +32302,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="458" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>1454</v>
       </c>
@@ -32383,7 +32387,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="460" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>1459</v>
       </c>
@@ -32427,7 +32431,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="461" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>1462</v>
       </c>
@@ -32471,7 +32475,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="462" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>1465</v>
       </c>
@@ -32515,7 +32519,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="463" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>1468</v>
       </c>
@@ -32559,7 +32563,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="464" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>1471</v>
       </c>
@@ -32647,7 +32651,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="466" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>1477</v>
       </c>
@@ -32691,7 +32695,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="467" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>1480</v>
       </c>
@@ -32735,7 +32739,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="468" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>1483</v>
       </c>
@@ -32823,7 +32827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="470" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>1489</v>
       </c>
@@ -32867,7 +32871,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="471" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>1492</v>
       </c>
@@ -32911,7 +32915,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="472" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>1495</v>
       </c>
@@ -33087,7 +33091,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="476" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>1507</v>
       </c>
@@ -33131,7 +33135,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="477" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>1510</v>
       </c>
@@ -33175,7 +33179,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="478" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>1513</v>
       </c>
@@ -33219,7 +33223,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="479" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>1516</v>
       </c>
@@ -33263,7 +33267,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="480" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>1519</v>
       </c>
@@ -33351,7 +33355,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="482" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>1525</v>
       </c>
@@ -33395,7 +33399,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="483" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>1528</v>
       </c>
@@ -33439,7 +33443,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="484" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>1531</v>
       </c>
@@ -33483,7 +33487,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="485" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>1534</v>
       </c>
@@ -33571,7 +33575,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="487" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>1540</v>
       </c>
@@ -33615,7 +33619,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="488" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>1543</v>
       </c>
@@ -33659,7 +33663,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="489" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>1546</v>
       </c>
@@ -33747,7 +33751,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="491" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>1552</v>
       </c>
@@ -33791,7 +33795,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="492" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>1555</v>
       </c>
@@ -33835,7 +33839,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="493" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>1558</v>
       </c>
@@ -33923,7 +33927,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="495" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>1564</v>
       </c>
@@ -33967,7 +33971,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="496" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>1567</v>
       </c>
@@ -34011,7 +34015,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="497" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>1570</v>
       </c>
@@ -34055,7 +34059,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="498" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>1574</v>
       </c>
@@ -34099,7 +34103,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="499" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>1577</v>
       </c>
@@ -34143,7 +34147,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="500" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>1580</v>
       </c>
@@ -34187,7 +34191,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="501" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>1584</v>
       </c>
@@ -34231,7 +34235,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="502" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>1587</v>
       </c>
@@ -34451,7 +34455,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="507" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>1603</v>
       </c>
@@ -34495,7 +34499,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="508" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>1606</v>
       </c>
@@ -34539,7 +34543,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="509" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>1609</v>
       </c>
@@ -34627,7 +34631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="511" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>1615</v>
       </c>
@@ -34671,7 +34675,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="512" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>1618</v>
       </c>
@@ -34715,7 +34719,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="513" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>1621</v>
       </c>
@@ -34759,7 +34763,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="514" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>1624</v>
       </c>
@@ -34803,7 +34807,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="515" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>1627</v>
       </c>
@@ -34847,7 +34851,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="516" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>1630</v>
       </c>
@@ -34935,7 +34939,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="518" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
         <v>1636</v>
       </c>
@@ -34979,7 +34983,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="519" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
         <v>1639</v>
       </c>
@@ -35023,7 +35027,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="520" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>1642</v>
       </c>
@@ -35067,7 +35071,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="521" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>1645</v>
       </c>
@@ -35111,7 +35115,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="522" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
         <v>1648</v>
       </c>
@@ -35155,7 +35159,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="523" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>1651</v>
       </c>
@@ -35196,7 +35200,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="524" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
         <v>1653</v>
       </c>
@@ -35325,7 +35329,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="527" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
         <v>1661</v>
       </c>
@@ -35369,7 +35373,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="528" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>1664</v>
       </c>
@@ -35545,7 +35549,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="532" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>1673</v>
       </c>
@@ -35677,7 +35681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="535" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>1682</v>
       </c>
@@ -35721,7 +35725,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="536" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>1685</v>
       </c>
@@ -35765,7 +35769,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="537" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>1688</v>
       </c>
@@ -35809,7 +35813,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="538" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>1691</v>
       </c>
@@ -35850,7 +35854,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="539" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>1693</v>
       </c>
@@ -35894,7 +35898,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="540" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>1696</v>
       </c>
@@ -35982,7 +35986,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="542" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>1702</v>
       </c>
@@ -36070,7 +36074,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="544" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>1709</v>
       </c>
@@ -36114,7 +36118,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="545" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
         <v>1712</v>
       </c>
@@ -36158,7 +36162,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="546" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
         <v>1715</v>
       </c>
@@ -36290,7 +36294,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="549" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
         <v>1724</v>
       </c>
@@ -36334,7 +36338,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="550" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
         <v>1727</v>
       </c>
@@ -36378,7 +36382,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="551" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
         <v>1730</v>
       </c>
@@ -36422,7 +36426,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="552" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
         <v>1733</v>
       </c>
@@ -36510,7 +36514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="554" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
         <v>1739</v>
       </c>
@@ -36554,7 +36558,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="555" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
         <v>1742</v>
       </c>
@@ -36686,7 +36690,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="558" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>1751</v>
       </c>
@@ -36730,7 +36734,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="559" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>1754</v>
       </c>
@@ -36774,7 +36778,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="560" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
         <v>1757</v>
       </c>
@@ -36862,7 +36866,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="562" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>1763</v>
       </c>
@@ -36906,7 +36910,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="563" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
         <v>1766</v>
       </c>
@@ -36950,7 +36954,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="564" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
         <v>1769</v>
       </c>
@@ -36994,7 +36998,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="565" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
         <v>1772</v>
       </c>
@@ -37038,7 +37042,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="566" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
         <v>1775</v>
       </c>
@@ -37082,7 +37086,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="567" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>1778</v>
       </c>
@@ -37170,7 +37174,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="569" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
         <v>1784</v>
       </c>
@@ -37258,7 +37262,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="571" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>1791</v>
       </c>
@@ -37302,7 +37306,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="572" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>1794</v>
       </c>
@@ -37522,7 +37526,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="577" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>1810</v>
       </c>
@@ -37566,7 +37570,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="578" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>1813</v>
       </c>
@@ -37610,7 +37614,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="579" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>1816</v>
       </c>
@@ -37742,7 +37746,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="582" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
         <v>1825</v>
       </c>
@@ -37786,7 +37790,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="583" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>1828</v>
       </c>
@@ -37830,7 +37834,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="584" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>1831</v>
       </c>
@@ -37874,7 +37878,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="585" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
         <v>1834</v>
       </c>
@@ -37918,7 +37922,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="586" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
         <v>1837</v>
       </c>
@@ -37962,7 +37966,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="587" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
         <v>1840</v>
       </c>
@@ -38050,7 +38054,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="589" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
         <v>1846</v>
       </c>
@@ -38094,7 +38098,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="590" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
         <v>1849</v>
       </c>
@@ -38138,7 +38142,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="591" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
         <v>1852</v>
       </c>
@@ -38182,7 +38186,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="592" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
         <v>1855</v>
       </c>
@@ -38226,7 +38230,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="593" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
         <v>1858</v>
       </c>
@@ -38270,7 +38274,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="594" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
         <v>1861</v>
       </c>
@@ -38314,7 +38318,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="595" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
         <v>1864</v>
       </c>
@@ -38402,7 +38406,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="597" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
         <v>1870</v>
       </c>
@@ -38446,7 +38450,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="598" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
         <v>1873</v>
       </c>
@@ -38534,7 +38538,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="600" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
         <v>1879</v>
       </c>
@@ -38710,7 +38714,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="604" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
         <v>1891</v>
       </c>
@@ -38842,7 +38846,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="607" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
         <v>1901</v>
       </c>
@@ -38886,7 +38890,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="608" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
         <v>1904</v>
       </c>
@@ -38930,7 +38934,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="609" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
         <v>1907</v>
       </c>
@@ -38971,7 +38975,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="610" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
         <v>1909</v>
       </c>
@@ -39015,7 +39019,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="611" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
         <v>1912</v>
       </c>
@@ -39059,7 +39063,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="612" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
         <v>1915</v>
       </c>
@@ -39103,7 +39107,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="613" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
         <v>1918</v>
       </c>
@@ -39147,7 +39151,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="614" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
         <v>1921</v>
       </c>
@@ -39191,7 +39195,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="615" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
         <v>1924</v>
       </c>
@@ -39235,7 +39239,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="616" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
         <v>1927</v>
       </c>
@@ -39279,7 +39283,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="617" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
         <v>1930</v>
       </c>
@@ -39323,7 +39327,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="618" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
         <v>1933</v>
       </c>
@@ -39455,7 +39459,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="621" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
         <v>1942</v>
       </c>
@@ -39543,7 +39547,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="623" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
         <v>1948</v>
       </c>
@@ -39587,7 +39591,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="624" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
         <v>1951</v>
       </c>
@@ -39631,7 +39635,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="625" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
         <v>1954</v>
       </c>
@@ -39848,7 +39852,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="630" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
         <v>1968</v>
       </c>
@@ -39892,7 +39896,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="631" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
         <v>1971</v>
       </c>
@@ -39977,7 +39981,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="633" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
         <v>1976</v>
       </c>
@@ -40021,7 +40025,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="634" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
         <v>1979</v>
       </c>
@@ -40065,7 +40069,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="635" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
         <v>1982</v>
       </c>
@@ -40109,7 +40113,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="636" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
         <v>1986</v>
       </c>
@@ -40153,7 +40157,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="637" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A637" t="s">
         <v>1989</v>
       </c>
@@ -40197,7 +40201,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="638" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
         <v>1992</v>
       </c>
@@ -40241,7 +40245,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="639" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A639" t="s">
         <v>1995</v>
       </c>
@@ -40285,7 +40289,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="640" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A640" t="s">
         <v>1998</v>
       </c>
@@ -40329,7 +40333,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="641" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A641" t="s">
         <v>2001</v>
       </c>
@@ -40373,7 +40377,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="642" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A642" t="s">
         <v>2004</v>
       </c>
@@ -40417,7 +40421,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="643" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A643" t="s">
         <v>2007</v>
       </c>
@@ -40461,7 +40465,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="644" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A644" t="s">
         <v>2010</v>
       </c>
@@ -40505,7 +40509,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="645" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A645" t="s">
         <v>2013</v>
       </c>
@@ -40549,7 +40553,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="646" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
         <v>2016</v>
       </c>
@@ -40593,7 +40597,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="647" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
         <v>2019</v>
       </c>
@@ -40637,7 +40641,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="648" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
         <v>2022</v>
       </c>
@@ -40725,7 +40729,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="650" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
         <v>2028</v>
       </c>
@@ -40769,7 +40773,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="651" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
         <v>2031</v>
       </c>
@@ -40857,7 +40861,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="653" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
         <v>2038</v>
       </c>
@@ -40901,7 +40905,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="654" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A654" t="s">
         <v>2041</v>
       </c>
@@ -40989,7 +40993,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="656" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A656" t="s">
         <v>2047</v>
       </c>
@@ -41033,7 +41037,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="657" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A657" t="s">
         <v>2050</v>
       </c>
@@ -41077,7 +41081,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="658" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A658" t="s">
         <v>2052</v>
       </c>
@@ -41121,7 +41125,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="659" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A659" t="s">
         <v>2055</v>
       </c>
@@ -41165,7 +41169,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="660" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A660" t="s">
         <v>2058</v>
       </c>
@@ -41209,7 +41213,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="661" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A661" t="s">
         <v>2061</v>
       </c>
@@ -41253,7 +41257,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="662" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A662" t="s">
         <v>2064</v>
       </c>
@@ -41341,7 +41345,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="664" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A664" t="s">
         <v>2070</v>
       </c>
@@ -41385,7 +41389,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="665" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A665" t="s">
         <v>2073</v>
       </c>
@@ -41517,7 +41521,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="668" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A668" t="s">
         <v>2082</v>
       </c>
@@ -41561,7 +41565,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="669" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A669" t="s">
         <v>2085</v>
       </c>
@@ -41605,7 +41609,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="670" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A670" t="s">
         <v>2088</v>
       </c>
@@ -41649,7 +41653,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="671" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A671" t="s">
         <v>2092</v>
       </c>
@@ -41737,7 +41741,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="673" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A673" t="s">
         <v>2099</v>
       </c>
@@ -41825,7 +41829,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="675" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A675" t="s">
         <v>2105</v>
       </c>
@@ -41869,7 +41873,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="676" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A676" t="s">
         <v>2108</v>
       </c>
@@ -41913,7 +41917,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="677" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A677" t="s">
         <v>2111</v>
       </c>
@@ -41957,7 +41961,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="678" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A678" t="s">
         <v>2114</v>
       </c>
@@ -42045,7 +42049,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="680" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A680" t="s">
         <v>2121</v>
       </c>
@@ -42133,7 +42137,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="682" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A682" t="s">
         <v>2127</v>
       </c>
@@ -42221,7 +42225,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="684" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A684" t="s">
         <v>2133</v>
       </c>
@@ -42265,7 +42269,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="685" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A685" t="s">
         <v>2136</v>
       </c>
@@ -42309,7 +42313,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="686" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A686" t="s">
         <v>2139</v>
       </c>
@@ -42441,7 +42445,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="689" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A689" t="s">
         <v>2149</v>
       </c>
@@ -42485,7 +42489,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="690" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A690" t="s">
         <v>2152</v>
       </c>
@@ -42529,7 +42533,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="691" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A691" t="s">
         <v>2155</v>
       </c>
@@ -42573,7 +42577,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="692" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A692" t="s">
         <v>2158</v>
       </c>
@@ -42617,7 +42621,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="693" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A693" t="s">
         <v>2161</v>
       </c>
@@ -42661,7 +42665,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="694" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A694" t="s">
         <v>2164</v>
       </c>
@@ -42705,7 +42709,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="695" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A695" t="s">
         <v>2167</v>
       </c>
@@ -42749,7 +42753,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="696" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A696" t="s">
         <v>2170</v>
       </c>
@@ -42790,7 +42794,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="697" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A697" t="s">
         <v>2172</v>
       </c>
@@ -42834,7 +42838,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="698" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A698" t="s">
         <v>2175</v>
       </c>
@@ -42878,7 +42882,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="699" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A699" t="s">
         <v>2178</v>
       </c>
@@ -42922,7 +42926,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="700" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A700" t="s">
         <v>2181</v>
       </c>
@@ -42966,7 +42970,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="701" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A701" t="s">
         <v>2183</v>
       </c>
@@ -43010,7 +43014,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="702" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A702" t="s">
         <v>2186</v>
       </c>
@@ -43054,7 +43058,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="703" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A703" t="s">
         <v>2189</v>
       </c>
@@ -43098,7 +43102,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="704" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A704" t="s">
         <v>2192</v>
       </c>
@@ -43142,7 +43146,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="705" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A705" t="s">
         <v>2195</v>
       </c>
@@ -43186,7 +43190,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="706" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A706" t="s">
         <v>2198</v>
       </c>
@@ -43274,7 +43278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="708" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A708" t="s">
         <v>2204</v>
       </c>
@@ -43318,7 +43322,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="709" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A709" t="s">
         <v>2207</v>
       </c>
@@ -43450,7 +43454,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="712" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A712" t="s">
         <v>2216</v>
       </c>
@@ -43494,7 +43498,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="713" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A713" t="s">
         <v>2219</v>
       </c>
@@ -43582,7 +43586,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="715" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A715" t="s">
         <v>2224</v>
       </c>
@@ -43670,7 +43674,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="717" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A717" t="s">
         <v>2230</v>
       </c>
@@ -43711,7 +43715,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="718" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A718" t="s">
         <v>2232</v>
       </c>
@@ -43843,7 +43847,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="721" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A721" t="s">
         <v>2242</v>
       </c>
@@ -43931,7 +43935,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="723" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A723" t="s">
         <v>2248</v>
       </c>
@@ -43975,7 +43979,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="724" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A724" t="s">
         <v>2251</v>
       </c>
@@ -44107,7 +44111,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="727" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A727" t="s">
         <v>2260</v>
       </c>
@@ -44151,7 +44155,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="728" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A728" t="s">
         <v>2263</v>
       </c>
@@ -44195,7 +44199,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="729" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A729" t="s">
         <v>2266</v>
       </c>
@@ -44283,7 +44287,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="731" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A731" t="s">
         <v>2272</v>
       </c>
@@ -44327,7 +44331,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="732" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A732" t="s">
         <v>2275</v>
       </c>
@@ -44503,7 +44507,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="736" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A736" t="s">
         <v>2289</v>
       </c>
@@ -44547,7 +44551,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="737" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A737" t="s">
         <v>2292</v>
       </c>
@@ -44591,7 +44595,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="738" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A738" t="s">
         <v>2295</v>
       </c>
@@ -44635,7 +44639,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="739" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A739" t="s">
         <v>2298</v>
       </c>
@@ -44679,7 +44683,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="740" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A740" t="s">
         <v>2301</v>
       </c>
@@ -44723,7 +44727,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="741" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A741" t="s">
         <v>2304</v>
       </c>
@@ -44855,7 +44859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="744" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A744" t="s">
         <v>2313</v>
       </c>
@@ -44943,7 +44947,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="746" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A746" t="s">
         <v>2320</v>
       </c>
@@ -44987,7 +44991,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="747" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A747" t="s">
         <v>2323</v>
       </c>
@@ -45075,7 +45079,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="749" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A749" t="s">
         <v>2329</v>
       </c>
@@ -45119,7 +45123,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="750" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A750" t="s">
         <v>2332</v>
       </c>
@@ -45163,7 +45167,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="751" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A751" t="s">
         <v>2335</v>
       </c>
@@ -45207,7 +45211,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="752" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A752" t="s">
         <v>2338</v>
       </c>
@@ -45295,7 +45299,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="754" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A754" t="s">
         <v>2344</v>
       </c>
@@ -45383,7 +45387,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="756" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A756" t="s">
         <v>2350</v>
       </c>
@@ -45427,7 +45431,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="757" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A757" t="s">
         <v>2353</v>
       </c>
@@ -45471,7 +45475,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="758" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A758" t="s">
         <v>2356</v>
       </c>
@@ -45515,7 +45519,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="759" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A759" t="s">
         <v>2359</v>
       </c>
@@ -45559,7 +45563,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="760" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A760" t="s">
         <v>2362</v>
       </c>
@@ -45691,7 +45695,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="763" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A763" t="s">
         <v>2372</v>
       </c>
@@ -45735,7 +45739,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="764" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A764" t="s">
         <v>2375</v>
       </c>
@@ -45823,7 +45827,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="766" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A766" t="s">
         <v>2381</v>
       </c>
@@ -45867,7 +45871,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="767" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A767" t="s">
         <v>2384</v>
       </c>
@@ -45911,7 +45915,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="768" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A768" t="s">
         <v>2387</v>
       </c>
@@ -45955,7 +45959,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="769" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A769" t="s">
         <v>2390</v>
       </c>
@@ -46043,7 +46047,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="771" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A771" t="s">
         <v>2397</v>
       </c>
@@ -46087,7 +46091,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="772" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A772" t="s">
         <v>2400</v>
       </c>
@@ -46131,7 +46135,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="773" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A773" t="s">
         <v>2403</v>
       </c>
@@ -46263,7 +46267,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="776" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A776" t="s">
         <v>2412</v>
       </c>
@@ -46351,7 +46355,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="778" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A778" t="s">
         <v>2418</v>
       </c>
@@ -46395,7 +46399,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="779" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A779" t="s">
         <v>2421</v>
       </c>
@@ -46439,7 +46443,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="780" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A780" t="s">
         <v>2424</v>
       </c>
@@ -46483,7 +46487,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="781" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A781" t="s">
         <v>2427</v>
       </c>
@@ -46527,7 +46531,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="782" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A782" t="s">
         <v>2430</v>
       </c>
@@ -46571,7 +46575,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="783" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A783" t="s">
         <v>2433</v>
       </c>
@@ -46612,7 +46616,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="784" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A784" t="s">
         <v>2435</v>
       </c>
@@ -46656,7 +46660,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="785" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A785" t="s">
         <v>2438</v>
       </c>
@@ -46700,7 +46704,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="786" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A786" t="s">
         <v>2441</v>
       </c>
@@ -46744,7 +46748,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="787" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A787" t="s">
         <v>2444</v>
       </c>
@@ -46832,7 +46836,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="789" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A789" t="s">
         <v>2450</v>
       </c>
@@ -46876,7 +46880,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="790" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A790" t="s">
         <v>2453</v>
       </c>
@@ -46920,7 +46924,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="791" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A791" t="s">
         <v>2456</v>
       </c>
@@ -47052,7 +47056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="794" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A794" t="s">
         <v>2466</v>
       </c>
@@ -47096,7 +47100,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="795" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A795" t="s">
         <v>2469</v>
       </c>
@@ -47140,7 +47144,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="796" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A796" t="s">
         <v>2472</v>
       </c>
@@ -47184,7 +47188,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="797" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A797" t="s">
         <v>2475</v>
       </c>
@@ -47228,7 +47232,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="798" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A798" t="s">
         <v>2478</v>
       </c>
@@ -47272,7 +47276,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="799" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A799" t="s">
         <v>2481</v>
       </c>
@@ -47316,7 +47320,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="800" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A800" t="s">
         <v>2484</v>
       </c>
@@ -47360,7 +47364,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="801" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A801" t="s">
         <v>2487</v>
       </c>
@@ -47448,7 +47452,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="803" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A803" t="s">
         <v>2493</v>
       </c>
@@ -47492,7 +47496,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="804" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A804" t="s">
         <v>2496</v>
       </c>
@@ -47624,7 +47628,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="807" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A807" t="s">
         <v>2505</v>
       </c>
@@ -47668,7 +47672,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="808" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A808" t="s">
         <v>2508</v>
       </c>
@@ -47712,7 +47716,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="809" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A809" t="s">
         <v>2511</v>
       </c>
@@ -47800,7 +47804,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="811" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A811" t="s">
         <v>2517</v>
       </c>
@@ -47844,7 +47848,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="812" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A812" t="s">
         <v>2520</v>
       </c>
@@ -47932,7 +47936,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="814" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A814" t="s">
         <v>2526</v>
       </c>
@@ -47976,7 +47980,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="815" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A815" t="s">
         <v>2529</v>
       </c>
@@ -48020,7 +48024,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="816" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A816" t="s">
         <v>2532</v>
       </c>
@@ -48064,7 +48068,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="817" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A817" t="s">
         <v>2535</v>
       </c>
@@ -48108,7 +48112,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="818" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A818" t="s">
         <v>2538</v>
       </c>
@@ -48196,7 +48200,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="820" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A820" t="s">
         <v>2544</v>
       </c>
@@ -48240,7 +48244,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="821" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A821" t="s">
         <v>2547</v>
       </c>
@@ -48284,7 +48288,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="822" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A822" t="s">
         <v>2550</v>
       </c>
@@ -48328,7 +48332,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="823" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A823" t="s">
         <v>2553</v>
       </c>
@@ -48416,7 +48420,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="825" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A825" t="s">
         <v>2559</v>
       </c>
@@ -48460,7 +48464,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="826" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A826" t="s">
         <v>2562</v>
       </c>
@@ -48504,7 +48508,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="827" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A827" t="s">
         <v>2565</v>
       </c>
@@ -48548,7 +48552,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="828" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A828" t="s">
         <v>2568</v>
       </c>
@@ -48636,7 +48640,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="830" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A830" t="s">
         <v>2574</v>
       </c>
@@ -48680,7 +48684,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="831" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A831" t="s">
         <v>2578</v>
       </c>
@@ -48724,7 +48728,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="832" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A832" t="s">
         <v>2581</v>
       </c>
@@ -48768,7 +48772,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="833" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A833" t="s">
         <v>2584</v>
       </c>
@@ -48812,7 +48816,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="834" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A834" t="s">
         <v>2587</v>
       </c>
@@ -48856,7 +48860,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="835" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A835" t="s">
         <v>2590</v>
       </c>
@@ -48900,7 +48904,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="836" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A836" t="s">
         <v>2593</v>
       </c>
@@ -48944,7 +48948,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="837" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A837" t="s">
         <v>2596</v>
       </c>
@@ -49032,7 +49036,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="839" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A839" t="s">
         <v>2602</v>
       </c>
@@ -49076,7 +49080,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="840" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A840" t="s">
         <v>2605</v>
       </c>
@@ -49120,7 +49124,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="841" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A841" t="s">
         <v>2608</v>
       </c>
@@ -49252,7 +49256,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="844" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A844" t="s">
         <v>2618</v>
       </c>
@@ -49296,7 +49300,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="845" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A845" t="s">
         <v>2621</v>
       </c>
@@ -49340,7 +49344,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="846" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A846" t="s">
         <v>2624</v>
       </c>
@@ -49428,7 +49432,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="848" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A848" t="s">
         <v>2630</v>
       </c>
@@ -49557,7 +49561,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="851" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A851" t="s">
         <v>2637</v>
       </c>
@@ -49645,7 +49649,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="853" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A853" t="s">
         <v>2643</v>
       </c>
@@ -49733,7 +49737,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="855" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A855" t="s">
         <v>2649</v>
       </c>
@@ -49777,7 +49781,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="856" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A856" t="s">
         <v>2652</v>
       </c>
@@ -49865,7 +49869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="858" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A858" t="s">
         <v>2658</v>
       </c>
@@ -49997,7 +50001,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="861" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A861" t="s">
         <v>2667</v>
       </c>
@@ -50041,7 +50045,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="862" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A862" t="s">
         <v>2670</v>
       </c>
@@ -50085,7 +50089,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="863" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A863" t="s">
         <v>2673</v>
       </c>
@@ -50129,7 +50133,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="864" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A864" t="s">
         <v>2676</v>
       </c>
@@ -50173,7 +50177,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="865" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A865" t="s">
         <v>2679</v>
       </c>
@@ -50214,7 +50218,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="866" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A866" t="s">
         <v>2681</v>
       </c>
@@ -50258,7 +50262,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="867" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A867" t="s">
         <v>2684</v>
       </c>
@@ -50302,7 +50306,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="868" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A868" t="s">
         <v>2688</v>
       </c>
@@ -50390,7 +50394,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="870" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A870" t="s">
         <v>2695</v>
       </c>
@@ -50434,7 +50438,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="871" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A871" t="s">
         <v>2698</v>
       </c>
@@ -50478,7 +50482,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="872" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A872" t="s">
         <v>2701</v>
       </c>
@@ -50610,7 +50614,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="875" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A875" t="s">
         <v>2711</v>
       </c>
@@ -50654,7 +50658,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="876" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A876" t="s">
         <v>2714</v>
       </c>
@@ -50698,7 +50702,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="877" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A877" t="s">
         <v>2717</v>
       </c>
@@ -50742,7 +50746,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="878" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A878" t="s">
         <v>2719</v>
       </c>
@@ -50830,7 +50834,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="880" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A880" t="s">
         <v>2725</v>
       </c>
@@ -50915,7 +50919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="882" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A882" t="s">
         <v>2730</v>
       </c>
@@ -50959,7 +50963,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="883" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A883" t="s">
         <v>2733</v>
       </c>
@@ -51091,7 +51095,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="886" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A886" t="s">
         <v>2743</v>
       </c>
@@ -51135,7 +51139,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="887" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A887" t="s">
         <v>2746</v>
       </c>
@@ -51179,7 +51183,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="888" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A888" t="s">
         <v>2749</v>
       </c>
@@ -51223,7 +51227,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="889" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A889" t="s">
         <v>2752</v>
       </c>
@@ -51267,7 +51271,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="890" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A890" t="s">
         <v>2755</v>
       </c>
@@ -51311,7 +51315,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="891" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A891" t="s">
         <v>2758</v>
       </c>
@@ -51399,7 +51403,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="893" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A893" t="s">
         <v>2764</v>
       </c>
@@ -51443,7 +51447,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="894" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A894" t="s">
         <v>2767</v>
       </c>
@@ -51487,7 +51491,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="895" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A895" t="s">
         <v>2770</v>
       </c>
@@ -51531,7 +51535,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="896" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A896" t="s">
         <v>2773</v>
       </c>
@@ -51575,7 +51579,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="897" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A897" t="s">
         <v>2776</v>
       </c>
@@ -51663,7 +51667,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="899" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A899" t="s">
         <v>2782</v>
       </c>
@@ -51795,7 +51799,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="902" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A902" t="s">
         <v>2791</v>
       </c>
@@ -51877,7 +51881,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="904" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A904" t="s">
         <v>2795</v>
       </c>
@@ -51921,7 +51925,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="905" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A905" t="s">
         <v>2797</v>
       </c>
@@ -51965,7 +51969,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="906" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A906" t="s">
         <v>2800</v>
       </c>
@@ -52050,7 +52054,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="908" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A908" t="s">
         <v>2805</v>
       </c>
@@ -52094,7 +52098,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="909" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A909" t="s">
         <v>2808</v>
       </c>
@@ -52270,7 +52274,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="913" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A913" t="s">
         <v>2820</v>
       </c>
@@ -52358,7 +52362,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="915" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A915" t="s">
         <v>2827</v>
       </c>
@@ -52402,7 +52406,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="916" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A916" t="s">
         <v>2830</v>
       </c>
@@ -52446,7 +52450,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="917" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A917" t="s">
         <v>2833</v>
       </c>
@@ -52490,7 +52494,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="918" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A918" t="s">
         <v>2837</v>
       </c>
@@ -52534,7 +52538,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="919" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A919" t="s">
         <v>2840</v>
       </c>
@@ -52622,7 +52626,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="921" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A921" t="s">
         <v>2846</v>
       </c>
@@ -52754,7 +52758,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="924" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A924" t="s">
         <v>2856</v>
       </c>
@@ -52798,7 +52802,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="925" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A925" t="s">
         <v>2859</v>
       </c>
@@ -52839,7 +52843,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="926" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A926" t="s">
         <v>2861</v>
       </c>
@@ -52883,7 +52887,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="927" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A927" t="s">
         <v>2864</v>
       </c>
@@ -52927,7 +52931,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="928" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A928" t="s">
         <v>2867</v>
       </c>
@@ -53012,7 +53016,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="930" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A930" t="s">
         <v>2873</v>
       </c>
@@ -53100,7 +53104,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="932" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A932" t="s">
         <v>2879</v>
       </c>
@@ -53144,7 +53148,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="933" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A933" t="s">
         <v>2882</v>
       </c>
@@ -53232,7 +53236,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="935" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A935" t="s">
         <v>2888</v>
       </c>
@@ -53320,7 +53324,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="937" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A937" t="s">
         <v>2894</v>
       </c>
@@ -53364,7 +53368,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="938" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A938" t="s">
         <v>2897</v>
       </c>
@@ -53408,7 +53412,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="939" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A939" t="s">
         <v>2900</v>
       </c>
@@ -53452,7 +53456,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="940" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A940" t="s">
         <v>2903</v>
       </c>
@@ -53496,7 +53500,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="941" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A941" t="s">
         <v>2906</v>
       </c>
@@ -53540,7 +53544,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="942" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A942" t="s">
         <v>2909</v>
       </c>
@@ -53628,7 +53632,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="944" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A944" t="s">
         <v>2915</v>
       </c>
@@ -53672,7 +53676,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="945" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A945" t="s">
         <v>2918</v>
       </c>
@@ -53716,7 +53720,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="946" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A946" t="s">
         <v>2921</v>
       </c>
@@ -53804,7 +53808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="948" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A948" t="s">
         <v>2927</v>
       </c>
@@ -53848,7 +53852,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="949" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A949" t="s">
         <v>2930</v>
       </c>
@@ -53892,7 +53896,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="950" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A950" t="s">
         <v>2933</v>
       </c>
@@ -53936,7 +53940,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="951" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A951" t="s">
         <v>2936</v>
       </c>
@@ -53980,7 +53984,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="952" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A952" t="s">
         <v>2939</v>
       </c>
@@ -54024,7 +54028,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="953" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A953" t="s">
         <v>2942</v>
       </c>
@@ -54068,7 +54072,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="954" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A954" t="s">
         <v>2945</v>
       </c>
@@ -54200,7 +54204,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="957" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A957" t="s">
         <v>2954</v>
       </c>
@@ -54332,7 +54336,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="960" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A960" t="s">
         <v>2963</v>
       </c>
@@ -54420,7 +54424,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="962" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A962" t="s">
         <v>2969</v>
       </c>
@@ -54596,7 +54600,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="966" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A966" t="s">
         <v>2981</v>
       </c>
@@ -54681,7 +54685,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="968" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A968" t="s">
         <v>2986</v>
       </c>
@@ -54725,7 +54729,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="969" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A969" t="s">
         <v>2988</v>
       </c>
@@ -54813,7 +54817,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="971" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A971" t="s">
         <v>2994</v>
       </c>
@@ -54857,7 +54861,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="972" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A972" t="s">
         <v>2997</v>
       </c>
@@ -54901,7 +54905,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="973" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A973" t="s">
         <v>3000</v>
       </c>
@@ -54945,7 +54949,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="974" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A974" t="s">
         <v>3004</v>
       </c>
@@ -55033,7 +55037,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="976" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A976" t="s">
         <v>3010</v>
       </c>
@@ -55077,7 +55081,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="977" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A977" t="s">
         <v>3013</v>
       </c>
@@ -55121,7 +55125,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="978" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A978" t="s">
         <v>3016</v>
       </c>
@@ -55209,7 +55213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="980" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A980" t="s">
         <v>3022</v>
       </c>
@@ -55253,7 +55257,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="981" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A981" t="s">
         <v>3025</v>
       </c>
@@ -55297,7 +55301,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="982" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A982" t="s">
         <v>3028</v>
       </c>
@@ -55385,7 +55389,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="984" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A984" t="s">
         <v>3034</v>
       </c>
@@ -55429,7 +55433,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="985" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A985" t="s">
         <v>3037</v>
       </c>
@@ -55473,7 +55477,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="986" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A986" t="s">
         <v>3040</v>
       </c>
@@ -55558,7 +55562,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="988" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A988" t="s">
         <v>3045</v>
       </c>
@@ -55646,7 +55650,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="990" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A990" t="s">
         <v>3051</v>
       </c>
@@ -55690,7 +55694,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="991" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A991" t="s">
         <v>3054</v>
       </c>
@@ -55734,7 +55738,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="992" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A992" t="s">
         <v>3057</v>
       </c>
@@ -55778,7 +55782,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="993" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A993" t="s">
         <v>3060</v>
       </c>
@@ -55822,7 +55826,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="994" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A994" t="s">
         <v>3063</v>
       </c>
@@ -55866,7 +55870,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="995" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A995" t="s">
         <v>3066</v>
       </c>
@@ -55910,7 +55914,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="996" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A996" t="s">
         <v>3069</v>
       </c>
@@ -55954,7 +55958,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="997" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A997" t="s">
         <v>3072</v>
       </c>
@@ -55998,7 +56002,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="998" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A998" t="s">
         <v>3075</v>
       </c>
@@ -56086,7 +56090,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1000" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1000" t="s">
         <v>3081</v>
       </c>
@@ -56130,7 +56134,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1001" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1001" t="s">
         <v>3084</v>
       </c>
@@ -56174,7 +56178,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1002" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1002" t="s">
         <v>3087</v>
       </c>
@@ -56218,7 +56222,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1003" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1003" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1003" t="s">
         <v>3091</v>
       </c>
@@ -56262,7 +56266,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1004" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1004" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1004" t="s">
         <v>3093</v>
       </c>
@@ -56306,7 +56310,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1005" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1005" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1005" t="s">
         <v>3095</v>
       </c>
@@ -56350,7 +56354,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1006" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1006" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1006" t="s">
         <v>3098</v>
       </c>
@@ -56394,7 +56398,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1007" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1007" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1007" t="s">
         <v>3101</v>
       </c>
@@ -56482,7 +56486,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1009" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1009" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1009" t="s">
         <v>3107</v>
       </c>
@@ -56526,7 +56530,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1010" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1010" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1010" t="s">
         <v>3110</v>
       </c>
@@ -56570,7 +56574,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1011" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1011" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1011" t="s">
         <v>3113</v>
       </c>
@@ -56614,7 +56618,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1012" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1012" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1012" t="s">
         <v>3116</v>
       </c>
@@ -56658,7 +56662,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1013" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1013" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1013" t="s">
         <v>3119</v>
       </c>
@@ -56702,7 +56706,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1014" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1014" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1014" t="s">
         <v>3122</v>
       </c>
@@ -56746,7 +56750,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1015" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1015" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1015" t="s">
         <v>3125</v>
       </c>
@@ -56790,7 +56794,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1016" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1016" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1016" t="s">
         <v>3128</v>
       </c>
@@ -56834,7 +56838,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1017" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1017" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1017" t="s">
         <v>3131</v>
       </c>
@@ -56922,7 +56926,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1019" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1019" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1019" t="s">
         <v>3137</v>
       </c>
@@ -56966,7 +56970,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1020" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1020" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1020" t="s">
         <v>3140</v>
       </c>
@@ -57010,7 +57014,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1021" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1021" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1021" t="s">
         <v>3143</v>
       </c>
@@ -57054,7 +57058,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1022" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1022" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1022" t="s">
         <v>3146</v>
       </c>
@@ -57098,7 +57102,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1023" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1023" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1023" t="s">
         <v>3149</v>
       </c>
@@ -57142,7 +57146,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1024" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1024" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1024" t="s">
         <v>3152</v>
       </c>
@@ -57186,7 +57190,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1025" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1025" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1025" t="s">
         <v>3155</v>
       </c>
@@ -57230,7 +57234,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1026" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1026" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1026" t="s">
         <v>3158</v>
       </c>
@@ -57274,7 +57278,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1027" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1027" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1027" t="s">
         <v>3161</v>
       </c>
@@ -57315,7 +57319,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1028" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1028" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1028" t="s">
         <v>3163</v>
       </c>
@@ -57359,7 +57363,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1029" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1029" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1029" t="s">
         <v>3166</v>
       </c>
@@ -57403,7 +57407,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1030" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1030" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1030" t="s">
         <v>3169</v>
       </c>
@@ -57491,7 +57495,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1032" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1032" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1032" t="s">
         <v>3175</v>
       </c>
@@ -57535,7 +57539,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1033" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1033" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1033" t="s">
         <v>3178</v>
       </c>
@@ -57579,7 +57583,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1034" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1034" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1034" t="s">
         <v>3181</v>
       </c>
@@ -57623,7 +57627,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1035" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1035" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1035" t="s">
         <v>3184</v>
       </c>
@@ -57711,7 +57715,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1037" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1037" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1037" t="s">
         <v>3190</v>
       </c>
@@ -57755,7 +57759,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1038" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1038" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1038" t="s">
         <v>3193</v>
       </c>
@@ -57799,7 +57803,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1039" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1039" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1039" t="s">
         <v>3196</v>
       </c>
@@ -57843,7 +57847,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1040" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1040" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1040" t="s">
         <v>3199</v>
       </c>
@@ -57887,7 +57891,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1041" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1041" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1041" t="s">
         <v>3202</v>
       </c>
@@ -57931,7 +57935,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1042" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1042" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1042" t="s">
         <v>3205</v>
       </c>
@@ -58016,7 +58020,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1044" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1044" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1044" t="s">
         <v>3210</v>
       </c>
@@ -58060,7 +58064,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1045" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1045" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1045" t="s">
         <v>3213</v>
       </c>
@@ -58148,7 +58152,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1047" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1047" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1047" t="s">
         <v>3219</v>
       </c>
@@ -58192,7 +58196,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1048" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1048" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1048" t="s">
         <v>3222</v>
       </c>
@@ -58236,7 +58240,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1049" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1049" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1049" t="s">
         <v>3225</v>
       </c>
@@ -58280,7 +58284,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1050" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1050" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1050" t="s">
         <v>3228</v>
       </c>
@@ -58412,7 +58416,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1053" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1053" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1053" t="s">
         <v>3237</v>
       </c>
@@ -58456,7 +58460,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1054" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1054" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1054" t="s">
         <v>3240</v>
       </c>
@@ -58500,7 +58504,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1055" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1055" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1055" t="s">
         <v>3243</v>
       </c>
@@ -58544,7 +58548,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1056" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1056" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1056" t="s">
         <v>3246</v>
       </c>
@@ -58588,7 +58592,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1057" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1057" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1057" t="s">
         <v>3249</v>
       </c>
@@ -58632,7 +58636,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1058" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1058" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1058" t="s">
         <v>3252</v>
       </c>
@@ -58676,7 +58680,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1059" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1059" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1059" t="s">
         <v>3255</v>
       </c>
@@ -58720,7 +58724,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1060" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1060" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1060" t="s">
         <v>3258</v>
       </c>
@@ -58808,7 +58812,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="1062" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1062" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1062" t="s">
         <v>3264</v>
       </c>
@@ -58896,7 +58900,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1064" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1064" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1064" t="s">
         <v>3270</v>
       </c>
@@ -58940,7 +58944,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1065" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1065" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1065" t="s">
         <v>3273</v>
       </c>
@@ -58984,7 +58988,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1066" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1066" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1066" t="s">
         <v>3276</v>
       </c>
@@ -59028,7 +59032,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1067" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1067" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1067" t="s">
         <v>3279</v>
       </c>
@@ -59072,7 +59076,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1068" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1068" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1068" t="s">
         <v>3282</v>
       </c>
@@ -59116,7 +59120,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1069" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1069" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1069" t="s">
         <v>3285</v>
       </c>
@@ -59160,7 +59164,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1070" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1070" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1070" t="s">
         <v>3288</v>
       </c>
@@ -59248,7 +59252,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1072" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1072" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1072" t="s">
         <v>3294</v>
       </c>
@@ -59336,7 +59340,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1074" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1074" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1074" t="s">
         <v>3300</v>
       </c>
@@ -59380,7 +59384,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1075" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1075" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1075" t="s">
         <v>3303</v>
       </c>
@@ -59424,7 +59428,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1076" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1076" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1076" t="s">
         <v>3306</v>
       </c>
@@ -59512,7 +59516,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1078" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1078" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1078" t="s">
         <v>3312</v>
       </c>
@@ -59556,7 +59560,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1079" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1079" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1079" t="s">
         <v>3315</v>
       </c>
@@ -59732,7 +59736,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1083" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1083" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1083" t="s">
         <v>3327</v>
       </c>
@@ -59776,7 +59780,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1084" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1084" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1084" t="s">
         <v>3330</v>
       </c>
@@ -59820,7 +59824,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1085" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1085" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1085" t="s">
         <v>3333</v>
       </c>
@@ -59864,7 +59868,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1086" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1086" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1086" t="s">
         <v>3336</v>
       </c>
@@ -59952,7 +59956,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1088" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1088" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1088" t="s">
         <v>3342</v>
       </c>
@@ -59996,7 +60000,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1089" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1089" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1089" t="s">
         <v>3345</v>
       </c>
@@ -60040,7 +60044,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1090" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1090" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1090" t="s">
         <v>3348</v>
       </c>
@@ -60084,7 +60088,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1091" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1091" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1091" t="s">
         <v>3352</v>
       </c>
@@ -60172,7 +60176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1093" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1093" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1093" t="s">
         <v>3358</v>
       </c>
@@ -60216,7 +60220,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1094" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1094" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1094" t="s">
         <v>3361</v>
       </c>
@@ -60260,7 +60264,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1095" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1095" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1095" t="s">
         <v>3364</v>
       </c>
@@ -60304,7 +60308,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1096" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1096" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1096" t="s">
         <v>3367</v>
       </c>
@@ -60392,7 +60396,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1098" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1098" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1098" t="s">
         <v>3373</v>
       </c>
@@ -60436,7 +60440,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1099" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1099" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1099" t="s">
         <v>3376</v>
       </c>
@@ -60480,7 +60484,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1100" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1100" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1100" t="s">
         <v>3379</v>
       </c>
@@ -60524,7 +60528,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1101" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1101" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1101" t="s">
         <v>3382</v>
       </c>
@@ -60656,7 +60660,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1104" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1104" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1104" t="s">
         <v>3391</v>
       </c>
@@ -60832,7 +60836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1108" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1108" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1108" t="s">
         <v>3403</v>
       </c>
@@ -60920,7 +60924,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1110" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1110" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1110" t="s">
         <v>3409</v>
       </c>
@@ -60964,7 +60968,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1111" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1111" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1111" t="s">
         <v>3412</v>
       </c>
@@ -61008,7 +61012,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1112" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1112" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1112" t="s">
         <v>3415</v>
       </c>
@@ -61052,7 +61056,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1113" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1113" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1113" t="s">
         <v>3418</v>
       </c>
@@ -61181,7 +61185,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1116" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1116" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1116" t="s">
         <v>3426</v>
       </c>
@@ -61225,7 +61229,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1117" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1117" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1117" t="s">
         <v>3429</v>
       </c>
@@ -61269,7 +61273,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1118" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1118" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1118" t="s">
         <v>3433</v>
       </c>
@@ -61357,7 +61361,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1120" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1120" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1120" t="s">
         <v>3439</v>
       </c>
@@ -61401,7 +61405,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1121" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1121" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1121" t="s">
         <v>3442</v>
       </c>
@@ -61489,7 +61493,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1123" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1123" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1123" t="s">
         <v>3448</v>
       </c>
@@ -61621,7 +61625,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1126" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1126" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1126" t="s">
         <v>3457</v>
       </c>
@@ -61665,7 +61669,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1127" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1127" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1127" t="s">
         <v>3460</v>
       </c>
@@ -61709,7 +61713,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1128" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1128" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1128" t="s">
         <v>3463</v>
       </c>
@@ -61753,7 +61757,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1129" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1129" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1129" t="s">
         <v>3466</v>
       </c>
@@ -61841,7 +61845,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1131" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1131" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1131" t="s">
         <v>3472</v>
       </c>
@@ -61929,7 +61933,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1133" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1133" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1133" t="s">
         <v>3478</v>
       </c>
@@ -61973,7 +61977,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1134" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1134" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1134" t="s">
         <v>3481</v>
       </c>
@@ -62017,7 +62021,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1135" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1135" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1135" t="s">
         <v>3484</v>
       </c>
@@ -62061,7 +62065,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1136" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1136" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1136" t="s">
         <v>3487</v>
       </c>
@@ -62105,7 +62109,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1137" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1137" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1137" t="s">
         <v>3490</v>
       </c>
@@ -62149,7 +62153,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1138" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1138" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1138" t="s">
         <v>3493</v>
       </c>
@@ -62193,7 +62197,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1139" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1139" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1139" t="s">
         <v>3496</v>
       </c>
@@ -62237,7 +62241,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1140" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1140" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1140" t="s">
         <v>3499</v>
       </c>
@@ -62281,7 +62285,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1141" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1141" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1141" t="s">
         <v>3502</v>
       </c>
@@ -62325,7 +62329,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1142" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1142" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1142" t="s">
         <v>3505</v>
       </c>
@@ -62369,7 +62373,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1143" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1143" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1143" t="s">
         <v>3508</v>
       </c>
@@ -62413,7 +62417,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1144" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1144" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1144" t="s">
         <v>3511</v>
       </c>
@@ -62501,7 +62505,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1146" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1146" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1146" t="s">
         <v>3517</v>
       </c>
@@ -62545,7 +62549,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1147" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1147" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1147" t="s">
         <v>3520</v>
       </c>
@@ -62677,7 +62681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1150" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1150" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1150" t="s">
         <v>3529</v>
       </c>
@@ -62721,7 +62725,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1151" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1151" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1151" t="s">
         <v>3532</v>
       </c>
@@ -62765,7 +62769,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1152" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1152" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1152" t="s">
         <v>3535</v>
       </c>
@@ -62853,7 +62857,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1154" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1154" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1154" t="s">
         <v>3541</v>
       </c>
@@ -62897,7 +62901,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1155" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1155" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1155" t="s">
         <v>3544</v>
       </c>
@@ -62982,7 +62986,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1157" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1157" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1157" t="s">
         <v>3549</v>
       </c>
@@ -63026,7 +63030,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1158" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1158" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1158" t="s">
         <v>3552</v>
       </c>
@@ -63158,7 +63162,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1161" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1161" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1161" t="s">
         <v>3561</v>
       </c>
@@ -63202,7 +63206,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1162" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1162" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1162" t="s">
         <v>3564</v>
       </c>
@@ -63246,7 +63250,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1163" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1163" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1163" t="s">
         <v>3567</v>
       </c>
@@ -63422,7 +63426,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1167" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1167" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1167" t="s">
         <v>3580</v>
       </c>
@@ -63466,7 +63470,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1168" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1168" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1168" t="s">
         <v>3583</v>
       </c>
@@ -63510,7 +63514,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1169" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1169" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1169" t="s">
         <v>3586</v>
       </c>
@@ -63554,7 +63558,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1170" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1170" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1170" t="s">
         <v>3589</v>
       </c>
@@ -63598,7 +63602,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1171" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1171" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1171" t="s">
         <v>3592</v>
       </c>
@@ -63686,7 +63690,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1173" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1173" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1173" t="s">
         <v>3598</v>
       </c>
@@ -63774,7 +63778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1175" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1175" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1175" t="s">
         <v>3604</v>
       </c>
@@ -63862,7 +63866,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1177" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1177" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1177" t="s">
         <v>3610</v>
       </c>
@@ -63906,7 +63910,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1178" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1178" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1178" t="s">
         <v>3613</v>
       </c>
@@ -63950,7 +63954,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1179" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1179" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1179" t="s">
         <v>3616</v>
       </c>
@@ -64038,7 +64042,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1181" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1181" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1181" t="s">
         <v>3622</v>
       </c>
@@ -64082,7 +64086,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1182" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1182" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1182" t="s">
         <v>3625</v>
       </c>
@@ -64170,7 +64174,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1184" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1184" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1184" t="s">
         <v>3631</v>
       </c>
@@ -64258,7 +64262,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1186" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1186" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1186" t="s">
         <v>3637</v>
       </c>
@@ -64302,7 +64306,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1187" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1187" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1187" t="s">
         <v>3640</v>
       </c>
@@ -64390,7 +64394,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1189" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1189" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1189" t="s">
         <v>3646</v>
       </c>
@@ -64434,7 +64438,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1190" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1190" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1190" t="s">
         <v>3649</v>
       </c>
@@ -64478,7 +64482,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1191" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1191" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1191" t="s">
         <v>3652</v>
       </c>
@@ -64522,7 +64526,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1192" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1192" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1192" t="s">
         <v>3655</v>
       </c>
@@ -64654,7 +64658,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1195" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1195" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1195" t="s">
         <v>3665</v>
       </c>
@@ -64739,7 +64743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1197" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1197" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1197" t="s">
         <v>3670</v>
       </c>
@@ -64871,7 +64875,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1200" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1200" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1200" t="s">
         <v>3679</v>
       </c>
@@ -64959,7 +64963,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1202" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1202" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1202" t="s">
         <v>3685</v>
       </c>
@@ -65003,7 +65007,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1203" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1203" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1203" t="s">
         <v>3688</v>
       </c>
@@ -65091,7 +65095,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1205" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1205" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1205" t="s">
         <v>3694</v>
       </c>
@@ -65135,7 +65139,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1206" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1206" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1206" t="s">
         <v>3697</v>
       </c>
@@ -65179,7 +65183,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1207" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1207" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1207" t="s">
         <v>3700</v>
       </c>
@@ -65223,7 +65227,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1208" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1208" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1208" t="s">
         <v>3703</v>
       </c>
@@ -65267,7 +65271,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1209" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1209" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1209" t="s">
         <v>3706</v>
       </c>
@@ -65311,7 +65315,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1210" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1210" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1210" t="s">
         <v>3709</v>
       </c>
@@ -65399,7 +65403,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="1212" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1212" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1212" t="s">
         <v>3715</v>
       </c>
@@ -65443,7 +65447,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1213" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1213" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1213" t="s">
         <v>3718</v>
       </c>
@@ -65487,7 +65491,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1214" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1214" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1214" t="s">
         <v>3721</v>
       </c>
@@ -65572,7 +65576,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="1216" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1216" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1216" t="s">
         <v>3726</v>
       </c>
@@ -65616,7 +65620,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1217" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1217" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1217" t="s">
         <v>3729</v>
       </c>
@@ -65704,7 +65708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1219" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1219" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1219" t="s">
         <v>3735</v>
       </c>
@@ -65792,7 +65796,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1221" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1221" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1221" t="s">
         <v>3741</v>
       </c>
@@ -65836,7 +65840,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1222" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1222" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1222" t="s">
         <v>3744</v>
       </c>
@@ -65880,7 +65884,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1223" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1223" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1223" t="s">
         <v>3747</v>
       </c>
@@ -65924,7 +65928,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1224" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1224" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1224" t="s">
         <v>3750</v>
       </c>
@@ -66012,7 +66016,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="1226" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1226" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1226" t="s">
         <v>3756</v>
       </c>
@@ -66056,7 +66060,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1227" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1227" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1227" t="s">
         <v>3759</v>
       </c>
@@ -66100,7 +66104,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1228" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1228" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1228" t="s">
         <v>3762</v>
       </c>
@@ -66188,7 +66192,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1230" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1230" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1230" t="s">
         <v>3768</v>
       </c>
@@ -66273,6 +66277,58 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="M1:M1235" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters blank="1">
+        <filter val="intermembrane space mitochondrial inner membrane mitochondrial intermembrane space mitochondrial outer membrane mitochondrial intermembrane space/mitochondrial inner membrane"/>
+        <filter val="intermembrane space mitochondrial intermembrane space"/>
+        <filter val="intermembrane space mitochondrial intermembrane space mitochondrial intermembrane space/mitochondrial inner membrane"/>
+        <filter val="intermembrane space mitochondrial intermembrane space mitochondrial matrix mitochondrial intermembrane space/mitochondrial inner membrane"/>
+        <filter val="intermembrane space mitochondrial intermembrane space mitochondrial outer membrane"/>
+        <filter val="intermembrane space mitochondrial intermembrane space mitochondrial outer membrane mitochondrial intermembrane space/mitochondrial inner membrane"/>
+        <filter val="mitochondrial inner membrane"/>
+        <filter val="mitochondrial inner membrane mitochondrial inner membraneintermembrane space mitochondrial intermembrane space"/>
+        <filter val="mitochondrial inner membrane mitochondrial inner membraneintermembrane space mitochondrial intermembrane space mitochondrial intermembrane space/mitochondrial inner membrane"/>
+        <filter val="mitochondrial inner membrane mitochondrial inner membraneintermembrane space mitochondrial intermembrane space mitochondrial matrix mitochondrial intermembrane space/mitochondrial inner membrane"/>
+        <filter val="mitochondrial inner membrane mitochondrial inner membraneintermembrane space mitochondrial matrix/mitochondrial inner membrane mitochondrial intermembrane space"/>
+        <filter val="mitochondrial inner membrane mitochondrial intermembrane space"/>
+        <filter val="mitochondrial inner membrane mitochondrial intermembrane space mitochondrial intermembrane space/mitochondrial inner membrane"/>
+        <filter val="mitochondrial inner membrane mitochondrial intermembrane space mitochondrial outer membrane"/>
+        <filter val="mitochondrial inner membrane mitochondrial intermembrane space mitochondrial outer membrane mitochondrial intermembrane space/mitochondrial inner membrane"/>
+        <filter val="mitochondrial inner membrane mitochondrial intermembrane space/mitochondrial inner membrane"/>
+        <filter val="mitochondrial inner membrane mitochondrial matrix"/>
+        <filter val="mitochondrial inner membrane mitochondrial matrix/mitochondrial inner membrane"/>
+        <filter val="mitochondrial inner membrane mitochondrial matrix/mitochondrial inner membrane mitochondrial intermembrane space"/>
+        <filter val="mitochondrial inner membrane mitochondrial matrix/mitochondrial inner membrane mitochondrial intermembrane space mitochondrial matrix"/>
+        <filter val="mitochondrial inner membrane mitochondrial matrix/mitochondrial inner membrane mitochondrial intermembrane space mitochondrial outer membrane"/>
+        <filter val="mitochondrial inner membrane mitochondrial matrix/mitochondrial inner membrane mitochondrial matrix"/>
+        <filter val="mitochondrial inner membrane mitochondrial matrix/mitochondrial inner membrane mitochondrial outer membrane"/>
+        <filter val="mitochondrial inner membrane mitochondrial nucleoid mitochondrial intermembrane space mitochondrial matrix"/>
+        <filter val="mitochondrial inner membrane mitochondrial nucleoid mitochondrial matrix mitochondrial intermembrane space/mitochondrial inner membrane"/>
+        <filter val="mitochondrial inner membrane mitochondrial nucleoid mitochondrial matrix/mitochondrial inner membrane mitochondrial matrix"/>
+        <filter val="mitochondrial inner membrane mitochondrial outer membrane"/>
+        <filter val="mitochondrial inner membrane mitochondrial outer membrane mitochondrial matrix"/>
+        <filter val="mitochondrial inner membrane mitochondrial outer membranemitochondrial inner membraneintermembrane space mitochondrial outer membrane mitochondrial intermembrane space/mitochondrial inner membrane"/>
+        <filter val="mitochondrial inner membraneintermembrane space mitochondrial matrix/mitochondrial inner membrane"/>
+        <filter val="mitochondrial intermembrane space mitochondrial matrix"/>
+        <filter val="mitochondrial intermembrane space/mitochondrial inner membrane"/>
+        <filter val="mitochondrial matrix"/>
+        <filter val="mitochondrial matrix mitochondrial matrix/mitochondrial inner membrane mitochondrial outer membrane mitochondrial nucleoid"/>
+        <filter val="mitochondrial matrix mitochondrial outer membrane mitochondrial nucleoid"/>
+        <filter val="mitochondrial matrix/mitochondrial inner membrane"/>
+        <filter val="mitochondrial matrix/mitochondrial inner membrane mitochondrial matrix"/>
+        <filter val="mitochondrial matrix/mitochondrial inner membrane mitochondrial outer membrane"/>
+        <filter val="mitochondrial nucleoid mitochondrial intermembrane space mitochondrial matrix"/>
+        <filter val="mitochondrial nucleoid mitochondrial matrix"/>
+        <filter val="mitochondrial nucleoid mitochondrial matrix/mitochondrial inner membrane mitochondrial matrix"/>
+        <filter val="mitochondrial outer membrane"/>
+        <filter val="mitochondrial outer membrane mitochondrial intermembrane space/mitochondrial inner membrane"/>
+        <filter val="mitochondrial outer membrane mitochondrial matrix"/>
+        <filter val="mitochondrial outer membrane mitochondrial outer membranemitochondrial matrix"/>
+        <filter val="mitochondrial outer membraneintermembrane space mitochondrial intermembrane space mitochondrial outer membrane"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>